--- a/zx_code_mstr-add.xlsx
+++ b/zx_code_mstr-add.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CoA_CS\CoA_CS-개발\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C164EBA6-A0B9-471D-B57B-B40A0E7F0695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B812A1-3A46-4CC2-819A-A347D0C54E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="795" windowWidth="29010" windowHeight="9030" xr2:uid="{6898B0EA-70F5-40CD-B275-910C14875918}"/>
+    <workbookView xWindow="2050" yWindow="1290" windowWidth="14400" windowHeight="7280" xr2:uid="{6898B0EA-70F5-40CD-B275-910C14875918}"/>
   </bookViews>
   <sheets>
     <sheet name="CodeList_View" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>Field Name</t>
   </si>
@@ -62,15 +62,6 @@
     <t>Char#2</t>
   </si>
   <si>
-    <t>CoA_CS_Start_Num</t>
-  </si>
-  <si>
-    <t>CoA NO 시작번호</t>
-  </si>
-  <si>
-    <t>Online: 301; 그외 사용자별로 구분(501,601,701,801,901)</t>
-  </si>
-  <si>
     <t>CoA_CS_Next_Num</t>
   </si>
   <si>
@@ -96,6 +87,10 @@
   </si>
   <si>
     <t>CoA_db\coa_cs.db</t>
+  </si>
+  <si>
+    <t>Not Used, dbconfig.jsan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -479,18 +474,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2DE628-5971-407C-96DE-6BCC8D550F0C}">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="52.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="7.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -513,7 +508,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -523,53 +518,51 @@
       <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3">
-        <v>505</v>
-      </c>
-      <c r="D3" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>12</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
       </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{bafec85b-e817-4277-86cb-66dc7d424280}" enabled="1" method="Standard" siteId="{aab2e961-1f45-4717-9a42-8f87802af9bd}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>